--- a/DELEGATES.xlsx
+++ b/DELEGATES.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="165">
   <si>
     <t>NAME</t>
   </si>
@@ -505,6 +505,15 @@
   </si>
   <si>
     <t>DR.KEVAL PATEL</t>
+  </si>
+  <si>
+    <t>DR. HIMANSHU PATEL</t>
+  </si>
+  <si>
+    <t>DR. RASHESH POTHIWALA</t>
+  </si>
+  <si>
+    <t>DR HIMANSHU PRAJAPTI</t>
   </si>
 </sst>
 </file>
@@ -582,7 +591,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -617,6 +626,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1107,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="5" bestFit="1" customWidth="1"/>
@@ -3062,6 +3077,48 @@
         <v>8401223239</v>
       </c>
     </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="5">
+        <v>139</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C141" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D141" s="13">
+        <v>9825396637</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="5">
+        <v>140</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D142" s="13">
+        <v>9825465815</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="5">
+        <v>141</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C143" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D143" s="13">
+        <v>9925075607</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DELEGATES.xlsx
+++ b/DELEGATES.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrutia\Downloads\Validation_GUI\Validation_GUI\Event_Guest_QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55517768-5A38-48CF-99D2-029A98D5F8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NGPA ORGANIZER LIST" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="166">
   <si>
     <t>NAME</t>
   </si>
@@ -514,12 +515,15 @@
   </si>
   <si>
     <t>DR HIMANSHU PRAJAPTI</t>
+  </si>
+  <si>
+    <t>DR. YASHPAL PATEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -591,7 +595,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -619,20 +623,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,7 +832,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -840,7 +841,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1121,14 +1122,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D143"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D144"/>
+  <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
@@ -3064,16 +3065,16 @@
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="11">
+      <c r="A139" s="9">
         <v>138</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C139" s="10" t="s">
+      <c r="C139" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D139" s="10">
+      <c r="D139" s="4">
         <v>8401223239</v>
       </c>
     </row>
@@ -3081,13 +3082,13 @@
       <c r="A141" s="5">
         <v>139</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C141" s="13" t="s">
+      <c r="C141" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D141" s="13">
+      <c r="D141" s="11">
         <v>9825396637</v>
       </c>
     </row>
@@ -3095,13 +3096,13 @@
       <c r="A142" s="5">
         <v>140</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="B142" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C142" s="13" t="s">
+      <c r="C142" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D142" s="13">
+      <c r="D142" s="11">
         <v>9825465815</v>
       </c>
     </row>
@@ -3109,14 +3110,28 @@
       <c r="A143" s="5">
         <v>141</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="B143" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D143" s="13">
+      <c r="D143" s="11">
         <v>9925075607</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="5">
+        <v>142</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D144" s="5">
+        <v>9898557441</v>
       </c>
     </row>
   </sheetData>

--- a/DELEGATES.xlsx
+++ b/DELEGATES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrutia\Downloads\Validation_GUI\Validation_GUI\Event_Guest_QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55517768-5A38-48CF-99D2-029A98D5F8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65365ABC-3EF1-44E8-87AF-D6006450CD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="167">
   <si>
     <t>NAME</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t>DR. YASHPAL PATEL</t>
+  </si>
+  <si>
+    <t>Dr D G Shah</t>
   </si>
 </sst>
 </file>
@@ -595,7 +598,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -631,9 +634,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1123,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.26953125" style="5" bestFit="1" customWidth="1"/>
@@ -3124,7 +3124,7 @@
       <c r="A144" s="5">
         <v>142</v>
       </c>
-      <c r="B144" s="12" t="s">
+      <c r="B144" s="10" t="s">
         <v>165</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -3132,6 +3132,20 @@
       </c>
       <c r="D144" s="5">
         <v>9898557441</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="5">
+        <v>143</v>
+      </c>
+      <c r="B145" t="s">
+        <v>166</v>
+      </c>
+      <c r="C145" t="s">
+        <v>69</v>
+      </c>
+      <c r="D145">
+        <v>9825925890</v>
       </c>
     </row>
   </sheetData>
